--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E409"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9009,6 +9009,48 @@
         <v>392</v>
       </c>
       <c r="E409" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>308</v>
+      </c>
+      <c r="C410" t="n">
+        <v>331.84</v>
+      </c>
+      <c r="D410" t="n">
+        <v>391.42</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>308</v>
+      </c>
+      <c r="C411" t="n">
+        <v>331.25</v>
+      </c>
+      <c r="D411" t="n">
+        <v>391.63</v>
+      </c>
+      <c r="E411" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9025,7 +9067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B432"/>
+  <dimension ref="A1:B434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13348,6 +13390,26 @@
       </c>
       <c r="B432" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -13516,28 +13578,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5463881650659068</v>
+        <v>-0.5648035543123775</v>
       </c>
       <c r="J2" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K2" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1237992092369229</v>
+        <v>0.1305117692033668</v>
       </c>
       <c r="M2" t="n">
-        <v>8.638380291058594</v>
+        <v>8.711555456448702</v>
       </c>
       <c r="N2" t="n">
-        <v>120.5508609778614</v>
+        <v>121.8772414547114</v>
       </c>
       <c r="O2" t="n">
-        <v>10.97956560970703</v>
+        <v>11.03980260035076</v>
       </c>
       <c r="P2" t="n">
-        <v>342.58008117371</v>
+        <v>342.7785318969136</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13594,28 +13656,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03468440683193728</v>
+        <v>-0.03406504697026802</v>
       </c>
       <c r="J3" t="n">
+        <v>410</v>
+      </c>
+      <c r="K3" t="n">
         <v>408</v>
       </c>
-      <c r="K3" t="n">
-        <v>406</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0002472518758057651</v>
+        <v>0.0002409076892536666</v>
       </c>
       <c r="M3" t="n">
-        <v>6.985194745002886</v>
+        <v>6.953001064570778</v>
       </c>
       <c r="N3" t="n">
-        <v>280.174958020217</v>
+        <v>278.8041800557828</v>
       </c>
       <c r="O3" t="n">
-        <v>16.7384275850576</v>
+        <v>16.69743034289357</v>
       </c>
       <c r="P3" t="n">
-        <v>331.8056633234949</v>
+        <v>331.7990424181393</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13672,28 +13734,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1680003242080292</v>
+        <v>-0.1677790150591953</v>
       </c>
       <c r="J4" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K4" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09239478841185</v>
+        <v>0.09301268835478893</v>
       </c>
       <c r="M4" t="n">
-        <v>3.087800146086772</v>
+        <v>3.07371080089424</v>
       </c>
       <c r="N4" t="n">
-        <v>16.16300766763452</v>
+        <v>16.08450329651096</v>
       </c>
       <c r="O4" t="n">
-        <v>4.020324323687645</v>
+        <v>4.010549001883777</v>
       </c>
       <c r="P4" t="n">
-        <v>395.7966022243011</v>
+        <v>395.7942564647391</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13731,7 +13793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E409"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24753,6 +24815,60 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-42.8014635367951,173.36233920799282</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-42.80198187338478,173.36166812246228</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-42.80283999768716,173.36160990762744</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-42.8014635367951,173.36233920799282</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-42.80197774550431,173.36166357970842</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-42.80284123730521,173.36161184712768</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E411"/>
+  <dimension ref="A1:E414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9051,6 +9051,69 @@
         <v>391.63</v>
       </c>
       <c r="E411" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>302.86</v>
+      </c>
+      <c r="C412" t="n">
+        <v>331.25</v>
+      </c>
+      <c r="D412" t="n">
+        <v>391.87</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>302.86</v>
+      </c>
+      <c r="C413" t="n">
+        <v>331.92</v>
+      </c>
+      <c r="D413" t="n">
+        <v>391.84</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="C414" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="D414" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="E414" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9067,7 +9130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B434"/>
+  <dimension ref="A1:B437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13410,6 +13473,36 @@
       </c>
       <c r="B434" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.4</v>
       </c>
     </row>
   </sheetData>
@@ -13578,28 +13671,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5648035543123775</v>
+        <v>-0.600154262754919</v>
       </c>
       <c r="J2" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1305117692033668</v>
+        <v>0.1419616706599583</v>
       </c>
       <c r="M2" t="n">
-        <v>8.711555456448702</v>
+        <v>8.878425476592215</v>
       </c>
       <c r="N2" t="n">
-        <v>121.8772414547114</v>
+        <v>125.7965290480665</v>
       </c>
       <c r="O2" t="n">
-        <v>11.03980260035076</v>
+        <v>11.21590518184183</v>
       </c>
       <c r="P2" t="n">
-        <v>342.7785318969136</v>
+        <v>343.1607778895953</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13656,28 +13749,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03406504697026802</v>
+        <v>-0.03266091439111345</v>
       </c>
       <c r="J3" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K3" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002409076892536666</v>
+        <v>0.0002247770686214512</v>
       </c>
       <c r="M3" t="n">
-        <v>6.953001064570778</v>
+        <v>6.906823742365591</v>
       </c>
       <c r="N3" t="n">
-        <v>278.8041800557828</v>
+        <v>276.7788908499248</v>
       </c>
       <c r="O3" t="n">
-        <v>16.69743034289357</v>
+        <v>16.63667307035649</v>
       </c>
       <c r="P3" t="n">
-        <v>331.7990424181393</v>
+        <v>331.7839657837843</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13734,28 +13827,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1677790150591953</v>
+        <v>-0.1668181351776254</v>
       </c>
       <c r="J4" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K4" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09301268835478893</v>
+        <v>0.09327494481970422</v>
       </c>
       <c r="M4" t="n">
-        <v>3.07371080089424</v>
+        <v>3.055600922882953</v>
       </c>
       <c r="N4" t="n">
-        <v>16.08450329651096</v>
+        <v>15.97159345542589</v>
       </c>
       <c r="O4" t="n">
-        <v>4.010549001883777</v>
+        <v>3.996447604489003</v>
       </c>
       <c r="P4" t="n">
-        <v>395.7942564647391</v>
+        <v>395.7840385042331</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13793,7 +13886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E411"/>
+  <dimension ref="A1:E414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24869,6 +24962,87 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-42.80142309358475,173.36230863453167</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-42.80197774550431,173.36166357970842</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-42.80284265401149,173.36161406369948</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-42.80142309358475,173.36230863453167</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-42.80198243309737,173.36166873842896</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-42.80284247692321,173.361613786628</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-42.80139586916207,173.36228805397528</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-42.80198705072613,173.3616738201544</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-42.802844956159106,173.36161766562887</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E414"/>
+  <dimension ref="A1:E415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9114,6 +9114,27 @@
         <v>392.26</v>
       </c>
       <c r="E414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>298.88</v>
+      </c>
+      <c r="C415" t="n">
+        <v>332.26</v>
+      </c>
+      <c r="D415" t="n">
+        <v>392</v>
+      </c>
+      <c r="E415" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9130,7 +9151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B437"/>
+  <dimension ref="A1:B438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13503,6 +13524,16 @@
       </c>
       <c r="B437" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -13671,28 +13702,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.600154262754919</v>
+        <v>-0.6129413949225397</v>
       </c>
       <c r="J2" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K2" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1419616706599583</v>
+        <v>0.1459105074286087</v>
       </c>
       <c r="M2" t="n">
-        <v>8.878425476592215</v>
+        <v>8.940978047893475</v>
       </c>
       <c r="N2" t="n">
-        <v>125.7965290480665</v>
+        <v>127.3956165454134</v>
       </c>
       <c r="O2" t="n">
-        <v>11.21590518184183</v>
+        <v>11.28696666715258</v>
       </c>
       <c r="P2" t="n">
-        <v>343.1607778895953</v>
+        <v>343.2995421965799</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13749,28 +13780,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03266091439111345</v>
+        <v>-0.03204751188120044</v>
       </c>
       <c r="J3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K3" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002247770686214512</v>
+        <v>0.0002174836376912515</v>
       </c>
       <c r="M3" t="n">
-        <v>6.906823742365591</v>
+        <v>6.892043134633182</v>
       </c>
       <c r="N3" t="n">
-        <v>276.7788908499248</v>
+        <v>276.111538607528</v>
       </c>
       <c r="O3" t="n">
-        <v>16.63667307035649</v>
+        <v>16.61660430435557</v>
       </c>
       <c r="P3" t="n">
-        <v>331.7839657837843</v>
+        <v>331.7773594383399</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13827,28 +13858,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1668181351776254</v>
+        <v>-0.1664961897993741</v>
       </c>
       <c r="J4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09327494481970422</v>
+        <v>0.09335786938273782</v>
       </c>
       <c r="M4" t="n">
-        <v>3.055600922882953</v>
+        <v>3.049623571211086</v>
       </c>
       <c r="N4" t="n">
-        <v>15.97159345542589</v>
+        <v>15.93425814838722</v>
       </c>
       <c r="O4" t="n">
-        <v>3.996447604489003</v>
+        <v>3.991773809772696</v>
       </c>
       <c r="P4" t="n">
-        <v>395.7840385042331</v>
+        <v>395.7806033121681</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13886,7 +13917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E414"/>
+  <dimension ref="A1:E415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25043,6 +25074,33 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-42.80139177762999,173.36228496094523</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-42.801984811875855,173.36167135628745</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-42.802843421394044,173.36161526434256</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
